--- a/public/showroom/data/订货政策-上传模板.xlsx
+++ b/public/showroom/data/订货政策-上传模板.xlsx
@@ -3,8 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="订货政策模板" sheetId="1" r:id="rId1"/>
-    <sheet name="填写说明" sheetId="2" r:id="rId2"/>
+    <sheet name="订货政策" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -398,262 +397,101 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:H3"/>
   <cols>
-    <col min="1" max="1" width="10.83203125" customWidth="1"/>
+    <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
-    <col min="3" max="3" width="16.83203125" customWidth="1"/>
-    <col min="4" max="4" width="24.83203125" customWidth="1"/>
-    <col min="5" max="5" width="18.83203125" customWidth="1"/>
-    <col min="6" max="6" width="16.83203125" customWidth="1"/>
-    <col min="7" max="7" width="36.83203125" customWidth="1"/>
-    <col min="8" max="8" width="36.83203125" customWidth="1"/>
-    <col min="9" max="9" width="24.83203125" customWidth="1"/>
-    <col min="10" max="10" width="24.83203125" customWidth="1"/>
-    <col min="11" max="11" width="24.83203125" customWidth="1"/>
+    <col min="3" max="3" width="18.83203125" customWidth="1"/>
+    <col min="4" max="4" width="28.83203125" customWidth="1"/>
+    <col min="5" max="5" width="20.83203125" customWidth="1"/>
+    <col min="6" max="6" width="14.83203125" customWidth="1"/>
+    <col min="7" max="7" width="40.83203125" customWidth="1"/>
+    <col min="8" max="8" width="20.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>各品牌订货政策-模板（7月版）</v>
+        <v>类目</v>
+      </c>
+      <c r="B1" t="str">
+        <v>国家</v>
+      </c>
+      <c r="C1" t="str">
+        <v>品牌</v>
+      </c>
+      <c r="D1" t="str">
+        <v>品牌风格</v>
+      </c>
+      <c r="E1" t="str">
+        <v>主力销售价格段</v>
+      </c>
+      <c r="F1" t="str">
+        <v>最新订货系列</v>
+      </c>
+      <c r="G1" t="str">
+        <v>品牌订货政策</v>
+      </c>
+      <c r="H1" t="str">
+        <v>品牌上新时间</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>类目</v>
+        <v/>
       </c>
       <c r="B2" t="str">
-        <v>国家</v>
+        <v/>
       </c>
       <c r="C2" t="str">
-        <v>品牌</v>
+        <v/>
       </c>
       <c r="D2" t="str">
-        <v>品牌风格</v>
+        <v/>
       </c>
       <c r="E2" t="str">
-        <v>主力销售价格段</v>
+        <v/>
       </c>
       <c r="F2" t="str">
-        <v>最新订货系列</v>
+        <v/>
       </c>
       <c r="G2" t="str">
-        <v>26SS订货政策门槛</v>
+        <v/>
       </c>
       <c r="H2" t="str">
-        <v>26AW订货政策</v>
-      </c>
-      <c r="I2" t="str">
-        <v>26AW品牌上新时间</v>
-      </c>
-      <c r="J2" t="str">
-        <v>非截单时间（沟通）</v>
-      </c>
-      <c r="K2" t="str">
-        <v>明星公关</v>
+        <v/>
       </c>
     </row>
     <row r="3" xml:space="preserve">
       <c r="A3" t="str">
-        <v>[例] 服装</v>
+        <v>服装</v>
       </c>
       <c r="B3" t="str">
-        <v>[例] 中国</v>
+        <v>中国</v>
       </c>
       <c r="C3" t="str">
         <v>[例] SEAMEW</v>
       </c>
       <c r="D3" t="str">
-        <v>[例] 当代艺术、极简克制</v>
+        <v>当代艺术、极简克制</v>
       </c>
       <c r="E3" t="str">
-        <v>[例] 主力客单：890-2999</v>
+        <v>主力客单：890-2999</v>
       </c>
       <c r="F3" t="str">
-        <v>[例] 2026AW</v>
+        <v>2026AW</v>
       </c>
       <c r="G3" t="str" xml:space="preserve">
-        <v xml:space="preserve">[例] 每款每色3件起订
-订货买手价 5W，4.5折</v>
-      </c>
-      <c r="H3" t="str" xml:space="preserve">
-        <v xml:space="preserve">[例] 每款每色3件起订
-订货买手价 8W，4.0折</v>
-      </c>
-      <c r="I3" t="str" xml:space="preserve">
-        <v xml:space="preserve">[例] 3个波段上新
-8月底/9月底/10月底</v>
-      </c>
-      <c r="J3" t="str">
-        <v>[例] 提前与品牌确认新订单货期</v>
-      </c>
-      <c r="K3" t="str">
-        <v>[例] 赵今麦、倪妮、赵露思</v>
+        <v xml:space="preserve">每款每色3件起订
+订货买手价  5W，4.5折
+订货买手价  8W，4折</v>
+      </c>
+      <c r="H3" t="str">
+        <v>第一波：8月底</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K3"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C14"/>
-  <cols>
-    <col min="1" max="1" width="20.83203125" customWidth="1"/>
-    <col min="2" max="2" width="40.83203125" customWidth="1"/>
-    <col min="3" max="3" width="40.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>填写说明</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>列名</v>
-      </c>
-      <c r="B3" t="str">
-        <v>填写要求</v>
-      </c>
-      <c r="C3" t="str">
-        <v>示例值</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>类目</v>
-      </c>
-      <c r="B4" t="str">
-        <v>填写服装/鞋履/配饰</v>
-      </c>
-      <c r="C4" t="str">
-        <v>服装</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>国家</v>
-      </c>
-      <c r="B5" t="str">
-        <v>填写国家或地区</v>
-      </c>
-      <c r="C5" t="str">
-        <v>中国</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>品牌</v>
-      </c>
-      <c r="B6" t="str">
-        <v>填写品牌全称</v>
-      </c>
-      <c r="C6" t="str">
-        <v>SEAMEW</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>品牌风格</v>
-      </c>
-      <c r="B7" t="str">
-        <v>一句话描述品牌风格定位</v>
-      </c>
-      <c r="C7" t="str">
-        <v>当代艺术、极简克制、人文气息</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>主力销售价格段</v>
-      </c>
-      <c r="B8" t="str">
-        <v>填写主力客单价范围</v>
-      </c>
-      <c r="C8" t="str">
-        <v>主力客单：890-2999</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>最新订货系列</v>
-      </c>
-      <c r="B9" t="str">
-        <v>填写最新订货系列名称</v>
-      </c>
-      <c r="C9" t="str">
-        <v>2026AW</v>
-      </c>
-    </row>
-    <row r="10" xml:space="preserve">
-      <c r="A10" t="str">
-        <v>26SS订货政策门槛</v>
-      </c>
-      <c r="B10" t="str">
-        <v>每款起订量、买手价折扣阶梯</v>
-      </c>
-      <c r="C10" t="str" xml:space="preserve">
-        <v xml:space="preserve">每款每色3件起订
-订货买手价 5W，4.5折</v>
-      </c>
-    </row>
-    <row r="11" xml:space="preserve">
-      <c r="A11" t="str">
-        <v>26AW订货政策</v>
-      </c>
-      <c r="B11" t="str">
-        <v>每款起订量、买手价折扣阶梯</v>
-      </c>
-      <c r="C11" t="str" xml:space="preserve">
-        <v xml:space="preserve">每款每色3件起订
-订货买手价 8W，4.0折</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>26AW品牌上新时间</v>
-      </c>
-      <c r="B12" t="str">
-        <v>新品上新时间及波段</v>
-      </c>
-      <c r="C12" t="str">
-        <v>3个波段上新：8月底/9月底/10月底</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>非截单时间（沟通）</v>
-      </c>
-      <c r="B13" t="str">
-        <v>与品牌沟通货期的要求</v>
-      </c>
-      <c r="C13" t="str">
-        <v>提前与品牌确认新订单货期</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>明星公关</v>
-      </c>
-      <c r="B14" t="str">
-        <v>明星/公关资源（可省略）</v>
-      </c>
-      <c r="C14" t="str">
-        <v>赵今麦、倪妮、赵露思</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H3"/>
   </ignoredErrors>
 </worksheet>
 </file>